--- a/artfynd/A 29984-2024 artfynd.xlsx
+++ b/artfynd/A 29984-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94189910</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412504.5748033967</v>
+        <v>412504</v>
       </c>
       <c r="R2" t="n">
-        <v>6656324.277063541</v>
+        <v>6656325</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94189901</v>
+        <v>112083113</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öst om Sörskog Skallberget NR, Vrm</t>
+          <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412552</v>
+        <v>412378</v>
       </c>
       <c r="R3" t="n">
-        <v>6656342</v>
+        <v>6656267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112083121</v>
+        <v>112083118</v>
       </c>
       <c r="B4" t="n">
-        <v>78706</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412967</v>
+        <v>412576</v>
       </c>
       <c r="R4" t="n">
-        <v>6656511</v>
+        <v>6656303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112083131</v>
+        <v>112083129</v>
       </c>
       <c r="B5" t="n">
-        <v>90849</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412955</v>
+        <v>413128</v>
       </c>
       <c r="R5" t="n">
-        <v>6656577</v>
+        <v>6656574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112083119</v>
+        <v>112083131</v>
       </c>
       <c r="B6" t="n">
-        <v>78706</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412969</v>
+        <v>412955</v>
       </c>
       <c r="R6" t="n">
-        <v>6656515</v>
+        <v>6656577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112083123</v>
+        <v>112083124</v>
       </c>
       <c r="B7" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412977</v>
+        <v>412986</v>
       </c>
       <c r="R7" t="n">
-        <v>6656498</v>
+        <v>6656479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112083129</v>
+        <v>112083114</v>
       </c>
       <c r="B8" t="n">
-        <v>90849</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413128</v>
+        <v>412352</v>
       </c>
       <c r="R8" t="n">
-        <v>6656574</v>
+        <v>6656282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,55 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112083116</v>
+        <v>112083120</v>
       </c>
       <c r="B9" t="n">
-        <v>4721</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412418</v>
+        <v>412969</v>
       </c>
       <c r="R9" t="n">
-        <v>6656333</v>
+        <v>6656515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112083113</v>
+        <v>112083122</v>
       </c>
       <c r="B10" t="n">
-        <v>94336</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412378</v>
+        <v>412967</v>
       </c>
       <c r="R10" t="n">
-        <v>6656267</v>
+        <v>6656511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112083130</v>
+        <v>112083123</v>
       </c>
       <c r="B11" t="n">
-        <v>78706</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413098</v>
+        <v>412977</v>
       </c>
       <c r="R11" t="n">
-        <v>6656604</v>
+        <v>6656498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,50 +1645,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112083124</v>
+        <v>112083116</v>
       </c>
       <c r="B12" t="n">
-        <v>77685</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412986</v>
+        <v>412418</v>
       </c>
       <c r="R12" t="n">
-        <v>6656479</v>
+        <v>6656334</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,15 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112083114</v>
+        <v>94189901</v>
       </c>
       <c r="B13" t="n">
-        <v>73807</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1758,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sörskog Skallberget, Vrm</t>
+          <t>Öst om Sörskog Skallberget NR, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412352</v>
+        <v>412552</v>
       </c>
       <c r="R13" t="n">
-        <v>6656281</v>
+        <v>6656342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,12 +1817,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,37 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112083122</v>
+        <v>112083119</v>
       </c>
       <c r="B14" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>412967</v>
+        <v>412969</v>
       </c>
       <c r="R14" t="n">
-        <v>6656511</v>
+        <v>6656515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,37 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112083120</v>
+        <v>112083121</v>
       </c>
       <c r="B15" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>412969</v>
+        <v>412967</v>
       </c>
       <c r="R15" t="n">
-        <v>6656515</v>
+        <v>6656511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,6 +2040,103 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112083130</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sörskog Skallberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>413098</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6656603</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29984-2024 artfynd.xlsx
+++ b/artfynd/A 29984-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189910</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083118</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083129</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083131</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083124</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083120</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083122</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083123</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083116</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189901</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083119</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083121</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,8 +2212,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083130</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>